--- a/school_2/ceilling/vor_spartac_2_ceilling.xlsx
+++ b/school_2/ceilling/vor_spartac_2_ceilling.xlsx
@@ -4,31 +4,33 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15624" windowHeight="8760" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15624" windowHeight="8760"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист2" sheetId="3" r:id="rId1"/>
-    <sheet name="Лист1" sheetId="1" r:id="rId2"/>
-    <sheet name="5.1ГКЛ" sheetId="18" r:id="rId3"/>
-    <sheet name="Table 1" sheetId="2" r:id="rId4"/>
-    <sheet name="2расчет" sheetId="9" r:id="rId5"/>
-    <sheet name="3вор" sheetId="4" r:id="rId6"/>
-    <sheet name="общая" sheetId="11" r:id="rId7"/>
-    <sheet name="3пом" sheetId="8" r:id="rId8"/>
-    <sheet name="3расчет" sheetId="6" r:id="rId9"/>
-    <sheet name="3.1-Пт" sheetId="14" r:id="rId10"/>
-    <sheet name="3.1" sheetId="15" r:id="rId11"/>
-    <sheet name="4.1-Пт" sheetId="16" r:id="rId12"/>
-    <sheet name="4.1" sheetId="17" r:id="rId13"/>
-    <sheet name="ПТ3эт" sheetId="12" r:id="rId14"/>
-    <sheet name="ПТ2эт" sheetId="13" r:id="rId15"/>
+    <sheet name="6.2ГКЛ" sheetId="20" r:id="rId1"/>
+    <sheet name="6.1ГКЛ" sheetId="19" r:id="rId2"/>
+    <sheet name="Лист2" sheetId="3" r:id="rId3"/>
+    <sheet name="Лист1" sheetId="1" r:id="rId4"/>
+    <sheet name="5.1ГКЛ" sheetId="18" r:id="rId5"/>
+    <sheet name="Table 1" sheetId="2" r:id="rId6"/>
+    <sheet name="2расчет" sheetId="9" r:id="rId7"/>
+    <sheet name="3вор" sheetId="4" r:id="rId8"/>
+    <sheet name="общая" sheetId="11" r:id="rId9"/>
+    <sheet name="3пом" sheetId="8" r:id="rId10"/>
+    <sheet name="3расчет" sheetId="6" r:id="rId11"/>
+    <sheet name="3.1-Пт" sheetId="14" r:id="rId12"/>
+    <sheet name="3.1" sheetId="15" r:id="rId13"/>
+    <sheet name="4.1-Пт" sheetId="16" r:id="rId14"/>
+    <sheet name="4.1" sheetId="17" r:id="rId15"/>
+    <sheet name="ПТ3эт" sheetId="12" r:id="rId16"/>
+    <sheet name="ПТ2эт" sheetId="13" r:id="rId17"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2218" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2314" uniqueCount="810">
   <si>
     <t>пт-6</t>
   </si>
@@ -8470,7 +8472,138 @@
     <t>Ед./шт.</t>
   </si>
   <si>
-    <t>Зашивка приборов Knauf Файерборд 12,5мм</t>
+    <t>Зашивка приборов Knauf Файерборд 12,5мм / 1 слой</t>
+  </si>
+  <si>
+    <t>Подготовка поверхности СКБ / потолка / базовая</t>
+  </si>
+  <si>
+    <t>Подготовка поверхности СКБ / потолка / финишная</t>
+  </si>
+  <si>
+    <t>Объем, м2</t>
+  </si>
+  <si>
+    <t>Строительные леса</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>2.006</t>
+  </si>
+  <si>
+    <t>10м(высота) * 2м(длина) * 4 шт =</t>
+  </si>
+  <si>
+    <t>7,5м(высота) * 2м(длина) * 4 шт =</t>
+  </si>
+  <si>
+    <t>2.058</t>
+  </si>
+  <si>
+    <t>7,5м(высота) * 2м(длина) * 8 шт =</t>
+  </si>
+  <si>
+    <t>2,5м(высота) * 2м(длина) * 4 шт =</t>
+  </si>
+  <si>
+    <t>Расчет (Строительные леса)</t>
+  </si>
+  <si>
+    <t>1.012</t>
+  </si>
+  <si>
+    <t>1.056</t>
+  </si>
+  <si>
+    <t>1.067</t>
+  </si>
+  <si>
+    <t>№ п.п</t>
+  </si>
+  <si>
+    <t>пом.</t>
+  </si>
+  <si>
+    <t>объем, м2.</t>
+  </si>
+  <si>
+    <t>Ведомость работ</t>
+  </si>
+  <si>
+    <t>Подготовка поверхности СКБ / потолка</t>
+  </si>
+  <si>
+    <t>опуск на стены 0.4 м</t>
+  </si>
+  <si>
+    <t>1 эт, (3 * 4 шт. *2 L *2.5 h)
+2 эт, (3 * 3 шт. *2 L *2.5 h)
+3 эт, (3 * 3 шт. *2 L *2.5 h)</t>
+  </si>
+  <si>
+    <t>Зашивка потолков 1 слой. Файерборд, 1, 2, 3 эт.</t>
+  </si>
+  <si>
+    <t>Монтаж подвесного потолка / с применением профиля ПП</t>
+  </si>
+  <si>
+    <t>базовый слой</t>
+  </si>
+  <si>
+    <t>финишная слой</t>
+  </si>
+  <si>
+    <t>Зашивка приборов Knauf Файерборд 12,5мм / 1 слой с двух сторон</t>
+  </si>
+  <si>
+    <t>2.5м(высота) * 2м(длина) * 13 шт =</t>
+  </si>
+  <si>
+    <t>(0.4 * 2 + 0,85) L * 1 h * 2 шт =</t>
+  </si>
+  <si>
+    <t>(0,6*2 + 1,3*2)L * 0,42 h * 1шт =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1м(выс) * 2м(дл) * 6 шт (лиф. шах) = </t>
+  </si>
+  <si>
+    <t>(0,7 + 0,25*2)L * 0,3 h * 2 шт =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,04 * 2 шт = </t>
+  </si>
+  <si>
+    <t>Зашивка Knauf Файерборд 12,5мм 
+/ 1 слой</t>
+  </si>
+  <si>
+    <t>Расчет (Облицовка)</t>
+  </si>
+  <si>
+    <t>Расчет (Облицовка вент. коробов - монтаж)</t>
+  </si>
+  <si>
+    <t>Расчет (Нижняя плоскость)</t>
+  </si>
+  <si>
+    <t>(2 L * 6 шт  + (0.4 * 2 + 0,85) L  * 2 шт + 
++ (0,6*2 + 1,3*2)L + (0,7 + 0,25*2) L )
+ * 0,08 ширина.</t>
+  </si>
+  <si>
+    <t>Подготовка поверхности СКБ / потолка / базовая 
+(17,62 * 2 + 8,08 + 1,72 "нижняя пл-ть" )</t>
+  </si>
+  <si>
+    <t>Подготовка поверхности СКБ / потолка / финишная  
+(17,62 * 2 + 8,08 + 1,72 "нижняя пл-ть" )</t>
+  </si>
+  <si>
+    <t>Лакокрасочные работы СКБ / окраска потолков / в 2 слоя
+(17,62 * 2 + 8,08 + 1,72 "нижняя пл-ть" )</t>
   </si>
 </sst>
 </file>
@@ -8948,7 +9081,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -9158,13 +9291,68 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="223">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -9683,6 +9871,86 @@
     <xf numFmtId="164" fontId="46" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="48" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="48" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -9691,6 +9959,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9708,20 +9982,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="48" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -10480,156 +10741,1265 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="9" tint="0.59999389629810485"/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="22.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="51" style="4" customWidth="1"/>
-    <col min="2" max="2" width="41.109375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="15.44140625" style="4" customWidth="1"/>
-    <col min="6" max="16384" width="22.33203125" style="4"/>
+    <col min="1" max="1" width="7.77734375" style="184" customWidth="1"/>
+    <col min="2" max="2" width="48.77734375" style="184" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="184" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" style="184" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="184"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="200" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
-      <c r="E1" s="186"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="B1" s="200"/>
+      <c r="C1" s="200"/>
+      <c r="D1" s="200"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="185" t="s">
+        <v>764</v>
+      </c>
+      <c r="B2" s="185" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="186" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="14" t="s">
+      <c r="D2" s="186" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="196">
+        <v>1</v>
+      </c>
+      <c r="B3" s="188" t="s">
+        <v>795</v>
+      </c>
+      <c r="C3" s="196" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="196">
+        <f>C15</f>
+        <v>17.62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="197">
         <v>1</v>
       </c>
-      <c r="E3" s="15">
-        <f>Лист1!B31</f>
-        <v>2126.1999999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="B4" s="188" t="s">
+        <v>802</v>
+      </c>
+      <c r="C4" s="197" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="197">
+        <f>C18</f>
+        <v>8.08</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="196">
+        <v>2</v>
+      </c>
+      <c r="B5" s="188" t="s">
+        <v>807</v>
+      </c>
+      <c r="C5" s="196" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="196">
+        <f>D3*2+D4 + C20</f>
+        <v>45.04</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="196">
+        <v>3</v>
+      </c>
+      <c r="B6" s="188" t="s">
+        <v>808</v>
+      </c>
+      <c r="C6" s="196" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="196">
+        <f>D5</f>
+        <v>45.04</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="196">
+        <v>4</v>
+      </c>
+      <c r="B7" s="188" t="s">
+        <v>809</v>
+      </c>
+      <c r="C7" s="196" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="196">
+        <f>D5</f>
+        <v>45.04</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="196">
+        <v>5</v>
+      </c>
+      <c r="B8" s="188" t="s">
+        <v>772</v>
+      </c>
+      <c r="C8" s="196" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="196">
+        <f>C23</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="201"/>
+      <c r="B9" s="201"/>
+      <c r="C9" s="201"/>
+      <c r="D9" s="201"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="200" t="s">
+        <v>804</v>
+      </c>
+      <c r="B10" s="200"/>
+      <c r="C10" s="200"/>
+      <c r="D10" s="200"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="198">
+        <v>1</v>
+      </c>
+      <c r="B11" s="185" t="s">
+        <v>799</v>
+      </c>
+      <c r="C11" s="185">
+        <v>12</v>
+      </c>
+      <c r="D11" s="197" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="198">
+        <v>2</v>
+      </c>
+      <c r="B12" s="198" t="s">
+        <v>797</v>
+      </c>
+      <c r="C12" s="185">
+        <v>3.3</v>
+      </c>
+      <c r="D12" s="197" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="198">
+        <v>3</v>
+      </c>
+      <c r="B13" s="198" t="s">
+        <v>798</v>
+      </c>
+      <c r="C13" s="185">
+        <v>1.6</v>
+      </c>
+      <c r="D13" s="197" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="198">
+        <v>4</v>
+      </c>
+      <c r="B14" s="198" t="s">
+        <v>800</v>
+      </c>
+      <c r="C14" s="185">
+        <v>0.72</v>
+      </c>
+      <c r="D14" s="197" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="202" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="203"/>
+      <c r="C15" s="198">
+        <f>SUM(C11:C14)</f>
+        <v>17.62</v>
+      </c>
+      <c r="D15" s="197" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="201"/>
+      <c r="B16" s="201"/>
+      <c r="C16" s="201"/>
+      <c r="D16" s="201"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="200" t="s">
+        <v>803</v>
+      </c>
+      <c r="B17" s="200"/>
+      <c r="C17" s="200"/>
+      <c r="D17" s="200"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="198">
+        <v>1</v>
+      </c>
+      <c r="B18" s="198" t="s">
+        <v>801</v>
+      </c>
+      <c r="C18" s="185">
+        <v>8.08</v>
+      </c>
+      <c r="D18" s="197" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="200" t="s">
+        <v>805</v>
+      </c>
+      <c r="B19" s="200"/>
+      <c r="C19" s="200"/>
+      <c r="D19" s="200"/>
+    </row>
+    <row r="20" spans="1:4" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="198">
+        <v>1</v>
+      </c>
+      <c r="B20" s="222" t="s">
+        <v>806</v>
+      </c>
+      <c r="C20" s="185">
+        <f>( 2*6 + (0.4*2 + 0.85) * 2 + (0.6*2+1.3*2) + (0.7 + 0.25 * 2) * 2) * 0.08</f>
+        <v>1.72</v>
+      </c>
+      <c r="D20" s="199" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="201"/>
+      <c r="B21" s="201"/>
+      <c r="C21" s="201"/>
+      <c r="D21" s="201"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="200" t="s">
+        <v>780</v>
+      </c>
+      <c r="B22" s="200"/>
+      <c r="C22" s="200"/>
+      <c r="D22" s="200"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="185" t="s">
+        <v>774</v>
+      </c>
+      <c r="B23" s="185" t="s">
+        <v>796</v>
+      </c>
+      <c r="C23" s="185">
+        <v>65</v>
+      </c>
+      <c r="D23" s="196" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A19:D19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10" style="29" customWidth="1"/>
+    <col min="2" max="16384" width="9.109375" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="12">
+        <v>3004</v>
+      </c>
+      <c r="B2" s="27">
+        <v>241.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="12">
+        <v>3007</v>
+      </c>
+      <c r="B3" s="27">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="12">
+        <v>3009</v>
+      </c>
+      <c r="B4" s="27">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="12">
+        <v>3012</v>
+      </c>
+      <c r="B5" s="27">
+        <v>233.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="12">
+        <v>3015</v>
+      </c>
+      <c r="B6" s="27">
+        <v>19.100000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="12">
+        <v>3017</v>
+      </c>
+      <c r="B7" s="27">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="12">
+        <v>3019</v>
+      </c>
+      <c r="B8" s="27">
+        <v>315.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="12">
+        <v>3023</v>
+      </c>
+      <c r="B9" s="27">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="12">
+        <v>3033</v>
+      </c>
+      <c r="B10" s="27">
+        <v>8.8999999999999986</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="12">
+        <v>3037</v>
+      </c>
+      <c r="B11" s="27">
+        <v>111.60000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="12">
+        <v>3041</v>
+      </c>
+      <c r="B12" s="27">
+        <v>159.80000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="12">
+        <v>3042</v>
+      </c>
+      <c r="B13" s="27">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="12">
+        <v>3043</v>
+      </c>
+      <c r="B14" s="27">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="12">
+        <v>3045</v>
+      </c>
+      <c r="B15" s="27">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="12">
+        <v>3046</v>
+      </c>
+      <c r="B16" s="27">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="12">
+        <v>3051</v>
+      </c>
+      <c r="B17" s="27">
+        <v>193.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="12">
+        <v>3053</v>
+      </c>
+      <c r="B18" s="27">
+        <v>198.20000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="12">
+        <v>3055</v>
+      </c>
+      <c r="B19" s="27">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="12">
+        <v>3057</v>
+      </c>
+      <c r="B20" s="27">
         <v>8</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="18">
-        <v>0.15</v>
-      </c>
-      <c r="E4" s="18">
-        <f>E3*D4</f>
-        <v>318.92999999999995</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="18">
-        <v>4.5</v>
-      </c>
-      <c r="E5" s="18">
-        <f>E3*D5</f>
-        <v>9567.9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="15">
-        <v>1</v>
-      </c>
-      <c r="E6" s="15">
-        <f>E3</f>
-        <v>2126.1999999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="12">
+        <v>3059</v>
+      </c>
+      <c r="B21" s="27">
+        <v>38.799999999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="12">
+        <v>3060</v>
+      </c>
+      <c r="B22" s="27">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="12">
+        <v>3061</v>
+      </c>
+      <c r="B23" s="27">
         <v>12</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="18">
-        <v>1.8</v>
-      </c>
-      <c r="E7" s="18">
-        <f>E6*D7</f>
-        <v>3827.16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="18">
-        <v>0.15</v>
-      </c>
-      <c r="E8" s="18">
-        <f>E6*D8</f>
-        <v>318.92999999999995</v>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="12">
+        <v>3062</v>
+      </c>
+      <c r="B24" s="27">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="12">
+        <v>3063</v>
+      </c>
+      <c r="B25" s="27">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="12">
+        <v>3064</v>
+      </c>
+      <c r="B26" s="27">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="12">
+        <v>3065</v>
+      </c>
+      <c r="B27" s="27">
+        <v>2.3000000000000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="12">
+        <v>3066</v>
+      </c>
+      <c r="B28" s="27">
+        <v>97.600000000000009</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="12">
+        <v>3067</v>
+      </c>
+      <c r="B29" s="27">
+        <v>14.299999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="31">
+        <f>SUM(B2:B29)</f>
+        <v>2056.7999999999997</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H47"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="52" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="52" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="60">
+        <v>3004</v>
+      </c>
+      <c r="B2" s="61">
+        <f>'3пом'!B2</f>
+        <v>241.1</v>
+      </c>
+      <c r="C2" s="61">
+        <v>244.1</v>
+      </c>
+      <c r="D2" s="52">
+        <v>244.9</v>
+      </c>
+      <c r="E2" s="62">
+        <f>B2-D2</f>
+        <v>-3.8000000000000114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="60">
+        <v>3007</v>
+      </c>
+      <c r="B3" s="61">
+        <f>'3пом'!B3</f>
+        <v>8.1</v>
+      </c>
+      <c r="C3" s="61">
+        <v>9.1</v>
+      </c>
+      <c r="D3" s="52">
+        <v>9.1</v>
+      </c>
+      <c r="E3" s="62">
+        <f t="shared" ref="E3:E29" si="0">B3-D3</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="60">
+        <v>3009</v>
+      </c>
+      <c r="B4" s="61">
+        <f>'3пом'!B4</f>
+        <v>22.8</v>
+      </c>
+      <c r="C4" s="61">
+        <v>23.5</v>
+      </c>
+      <c r="D4" s="52">
+        <v>23.5</v>
+      </c>
+      <c r="E4" s="62">
+        <f t="shared" si="0"/>
+        <v>-0.69999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="63">
+        <v>3012</v>
+      </c>
+      <c r="B5" s="64">
+        <f>'3пом'!B5</f>
+        <v>233.5</v>
+      </c>
+      <c r="C5" s="64">
+        <v>470.2</v>
+      </c>
+      <c r="D5" s="65">
+        <v>235.7</v>
+      </c>
+      <c r="E5" s="62">
+        <f t="shared" si="0"/>
+        <v>-2.1999999999999886</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="60">
+        <v>3015</v>
+      </c>
+      <c r="B6" s="61">
+        <f>'3пом'!B6</f>
+        <v>19.100000000000001</v>
+      </c>
+      <c r="C6" s="61">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="D6" s="52">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="E6" s="62">
+        <f t="shared" si="0"/>
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="60">
+        <v>3017</v>
+      </c>
+      <c r="B7" s="61">
+        <f>'3пом'!B7</f>
+        <v>9.4</v>
+      </c>
+      <c r="C7" s="61">
+        <v>10.3</v>
+      </c>
+      <c r="D7" s="52">
+        <v>10.3</v>
+      </c>
+      <c r="E7" s="62">
+        <f t="shared" si="0"/>
+        <v>-0.90000000000000036</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="60">
+        <v>3019</v>
+      </c>
+      <c r="B8" s="61">
+        <f>'3пом'!B8</f>
+        <v>315.5</v>
+      </c>
+      <c r="C8" s="61">
+        <v>321.8</v>
+      </c>
+      <c r="D8" s="52">
+        <v>320.39999999999998</v>
+      </c>
+      <c r="E8" s="62">
+        <f t="shared" si="0"/>
+        <v>-4.8999999999999773</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="63">
+        <v>3023</v>
+      </c>
+      <c r="B9" s="64">
+        <f>'3пом'!B9</f>
+        <v>185.9</v>
+      </c>
+      <c r="C9" s="64">
+        <v>364.3</v>
+      </c>
+      <c r="D9" s="65">
+        <v>188.6</v>
+      </c>
+      <c r="E9" s="62">
+        <f t="shared" si="0"/>
+        <v>-2.6999999999999886</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="60">
+        <v>3033</v>
+      </c>
+      <c r="B10" s="61">
+        <f>'3пом'!B10</f>
+        <v>8.8999999999999986</v>
+      </c>
+      <c r="C10" s="61">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="D10" s="52">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E10" s="62">
+        <f t="shared" si="0"/>
+        <v>-0.30000000000000071</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="63">
+        <v>3037</v>
+      </c>
+      <c r="B11" s="64">
+        <f>'3пом'!B11</f>
+        <v>111.60000000000001</v>
+      </c>
+      <c r="C11" s="64">
+        <v>232.5</v>
+      </c>
+      <c r="D11" s="65">
+        <v>116.4</v>
+      </c>
+      <c r="E11" s="62">
+        <f t="shared" si="0"/>
+        <v>-4.7999999999999972</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="63">
+        <v>3041</v>
+      </c>
+      <c r="B12" s="64">
+        <f>'3пом'!B12</f>
+        <v>159.80000000000001</v>
+      </c>
+      <c r="C12" s="64">
+        <v>331.2</v>
+      </c>
+      <c r="D12" s="65">
+        <v>165.8</v>
+      </c>
+      <c r="E12" s="62">
+        <f t="shared" si="0"/>
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="60">
+        <v>3042</v>
+      </c>
+      <c r="B13" s="61">
+        <f>'3пом'!B13</f>
+        <v>21.4</v>
+      </c>
+      <c r="C13" s="61">
+        <v>22.2</v>
+      </c>
+      <c r="D13" s="52">
+        <v>22.2</v>
+      </c>
+      <c r="E13" s="62">
+        <f t="shared" si="0"/>
+        <v>-0.80000000000000071</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="60">
+        <v>3043</v>
+      </c>
+      <c r="B14" s="61">
+        <f>'3пом'!B14</f>
+        <v>21.8</v>
+      </c>
+      <c r="C14" s="61">
+        <v>22.1</v>
+      </c>
+      <c r="D14" s="52">
+        <v>22.1</v>
+      </c>
+      <c r="E14" s="62">
+        <f t="shared" si="0"/>
+        <v>-0.30000000000000071</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="60">
+        <v>3045</v>
+      </c>
+      <c r="B15" s="61">
+        <f>'3пом'!B15</f>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="C15" s="61">
+        <v>5.6</v>
+      </c>
+      <c r="D15" s="52">
+        <v>5.6</v>
+      </c>
+      <c r="E15" s="62">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="60">
+        <v>3046</v>
+      </c>
+      <c r="B16" s="61">
+        <f>'3пом'!B16</f>
+        <v>9</v>
+      </c>
+      <c r="C16" s="61">
+        <v>9.1</v>
+      </c>
+      <c r="D16" s="52">
+        <v>9.1</v>
+      </c>
+      <c r="E16" s="62">
+        <f t="shared" si="0"/>
+        <v>-9.9999999999999645E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="63">
+        <v>3051</v>
+      </c>
+      <c r="B17" s="64">
+        <f>'3пом'!B17</f>
+        <v>193.7</v>
+      </c>
+      <c r="C17" s="64">
+        <v>363.8</v>
+      </c>
+      <c r="D17" s="65">
+        <v>198.1</v>
+      </c>
+      <c r="E17" s="62">
+        <f t="shared" si="0"/>
+        <v>-4.4000000000000057</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="60">
+        <v>3053</v>
+      </c>
+      <c r="B18" s="61">
+        <f>'3пом'!B18</f>
+        <v>198.20000000000002</v>
+      </c>
+      <c r="C18" s="61">
+        <v>200.9</v>
+      </c>
+      <c r="D18" s="52">
+        <v>200.9</v>
+      </c>
+      <c r="E18" s="62">
+        <f t="shared" si="0"/>
+        <v>-2.6999999999999886</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="60">
+        <v>3055</v>
+      </c>
+      <c r="B19" s="61">
+        <f>'3пом'!B19</f>
+        <v>13.8</v>
+      </c>
+      <c r="C19" s="61">
+        <v>14.5</v>
+      </c>
+      <c r="D19" s="52">
+        <v>14.5</v>
+      </c>
+      <c r="E19" s="62">
+        <f t="shared" si="0"/>
+        <v>-0.69999999999999929</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="60">
+        <v>3057</v>
+      </c>
+      <c r="B20" s="61">
+        <f>'3пом'!B20</f>
+        <v>8</v>
+      </c>
+      <c r="C20" s="61">
+        <v>8.6</v>
+      </c>
+      <c r="D20" s="52">
+        <v>8.6</v>
+      </c>
+      <c r="E20" s="62">
+        <f t="shared" si="0"/>
+        <v>-0.59999999999999964</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="60">
+        <v>3059</v>
+      </c>
+      <c r="B21" s="61">
+        <f>'3пом'!B21</f>
+        <v>38.799999999999997</v>
+      </c>
+      <c r="C21" s="61">
+        <v>39</v>
+      </c>
+      <c r="D21" s="52">
+        <v>39</v>
+      </c>
+      <c r="E21" s="62">
+        <f t="shared" si="0"/>
+        <v>-0.20000000000000284</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="60">
+        <v>3060</v>
+      </c>
+      <c r="B22" s="61">
+        <f>'3пом'!B22</f>
+        <v>7.5</v>
+      </c>
+      <c r="C22" s="61">
+        <v>7.6</v>
+      </c>
+      <c r="D22" s="52">
+        <v>7.6</v>
+      </c>
+      <c r="E22" s="62">
+        <f t="shared" si="0"/>
+        <v>-9.9999999999999645E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="60">
+        <v>3061</v>
+      </c>
+      <c r="B23" s="61">
+        <f>'3пом'!B23</f>
+        <v>12</v>
+      </c>
+      <c r="C23" s="61">
+        <v>12.8</v>
+      </c>
+      <c r="D23" s="52">
+        <v>12.8</v>
+      </c>
+      <c r="E23" s="62">
+        <f t="shared" si="0"/>
+        <v>-0.80000000000000071</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="60">
+        <v>3062</v>
+      </c>
+      <c r="B24" s="61">
+        <f>'3пом'!B24</f>
+        <v>11.5</v>
+      </c>
+      <c r="C24" s="61">
+        <v>11.8</v>
+      </c>
+      <c r="D24" s="62">
+        <f>B24</f>
+        <v>11.5</v>
+      </c>
+      <c r="E24" s="62">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="60">
+        <v>3063</v>
+      </c>
+      <c r="B25" s="61">
+        <f>'3пом'!B25</f>
+        <v>72</v>
+      </c>
+      <c r="C25" s="61">
+        <v>72.8</v>
+      </c>
+      <c r="D25" s="62">
+        <f t="shared" ref="D25:D27" si="1">B25</f>
+        <v>72</v>
+      </c>
+      <c r="E25" s="62">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="60">
+        <v>3064</v>
+      </c>
+      <c r="B26" s="61">
+        <f>'3пом'!B26</f>
+        <v>14.6</v>
+      </c>
+      <c r="C26" s="61">
+        <v>15.6</v>
+      </c>
+      <c r="D26" s="62">
+        <f t="shared" si="1"/>
+        <v>14.6</v>
+      </c>
+      <c r="E26" s="62">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="60">
+        <v>3065</v>
+      </c>
+      <c r="B27" s="61">
+        <f>'3пом'!B27</f>
+        <v>2.3000000000000003</v>
+      </c>
+      <c r="C27" s="61">
+        <v>3.2</v>
+      </c>
+      <c r="D27" s="62">
+        <f t="shared" si="1"/>
+        <v>2.3000000000000003</v>
+      </c>
+      <c r="E27" s="62">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="60">
+        <v>3066</v>
+      </c>
+      <c r="B28" s="61">
+        <f>'3пом'!B28</f>
+        <v>97.600000000000009</v>
+      </c>
+      <c r="C28" s="61">
+        <v>102.2</v>
+      </c>
+      <c r="D28" s="52">
+        <v>101.7</v>
+      </c>
+      <c r="E28" s="62">
+        <f t="shared" si="0"/>
+        <v>-4.0999999999999943</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="60">
+        <v>3067</v>
+      </c>
+      <c r="B29" s="61">
+        <f>'3пом'!B29</f>
+        <v>14.299999999999999</v>
+      </c>
+      <c r="C29" s="61">
+        <v>15.3</v>
+      </c>
+      <c r="D29" s="52">
+        <v>15.2</v>
+      </c>
+      <c r="E29" s="62">
+        <f t="shared" si="0"/>
+        <v>-0.90000000000000036</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B30" s="20">
+        <f>SUM(B2:B29)</f>
+        <v>2056.7999999999997</v>
+      </c>
+      <c r="C30" s="20">
+        <f>SUM(C2:C29)</f>
+        <v>2962.9</v>
+      </c>
+      <c r="D30" s="20">
+        <f t="shared" ref="D30:E30" si="2">SUM(D2:D29)</f>
+        <v>2101.2999999999993</v>
+      </c>
+      <c r="E30" s="20">
+        <f t="shared" si="2"/>
+        <v>-44.49999999999995</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D31" s="58"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="25">
+        <v>3006</v>
+      </c>
+      <c r="B33" s="26"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="21">
+        <v>3016</v>
+      </c>
+      <c r="B34" s="22"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="25">
+        <v>3020</v>
+      </c>
+      <c r="B35" s="26"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="25">
+        <v>3024</v>
+      </c>
+      <c r="B36" s="26"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="25">
+        <v>3034</v>
+      </c>
+      <c r="B37" s="26"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="23">
+        <v>3047</v>
+      </c>
+      <c r="B38" s="24"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="21">
+        <v>3052</v>
+      </c>
+      <c r="B39" s="22"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G40" t="s">
+        <v>28</v>
+      </c>
+      <c r="H40" s="20">
+        <f>B17+B18+B21+B22+B23+B24</f>
+        <v>461.7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G41" t="s">
+        <v>29</v>
+      </c>
+      <c r="H41" s="20">
+        <f>SUM(B11:B16)+B27</f>
+        <v>330.50000000000006</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G42" t="s">
+        <v>30</v>
+      </c>
+      <c r="H42" s="44">
+        <f>B10+B28+B19+B20+B26</f>
+        <v>142.9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G43" t="s">
+        <v>31</v>
+      </c>
+      <c r="H43" s="20">
+        <f>B8+B9+B25</f>
+        <v>573.4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G44" t="s">
+        <v>32</v>
+      </c>
+      <c r="H44" s="20">
+        <f>SUM(B5:B7)+B29</f>
+        <v>276.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G45" t="s">
+        <v>33</v>
+      </c>
+      <c r="H45" s="20">
+        <f>SUM(B2:B4)</f>
+        <v>272</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H46" s="20">
+        <f>B30</f>
+        <v>2056.7999999999997</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H47" s="20">
+        <f>SUM(H40:H45)-H46</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
@@ -10702,7 +12072,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
@@ -10793,7 +12163,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
@@ -10866,7 +12236,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
@@ -10958,7 +12328,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="6" tint="0.39997558519241921"/>
@@ -12474,7 +13844,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="6" tint="0.39997558519241921"/>
@@ -14344,6 +15714,493 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.88671875" style="184" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.88671875" style="184" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="184" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" style="184" customWidth="1"/>
+    <col min="5" max="5" width="32.88671875" style="184" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" style="184" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" style="184" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="184"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="200" t="s">
+        <v>787</v>
+      </c>
+      <c r="B1" s="200"/>
+      <c r="C1" s="200"/>
+      <c r="D1" s="200"/>
+      <c r="E1" s="200"/>
+      <c r="F1" s="200"/>
+      <c r="G1" s="200"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="185" t="s">
+        <v>764</v>
+      </c>
+      <c r="B2" s="209" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="210"/>
+      <c r="D2" s="211"/>
+      <c r="E2" s="193" t="s">
+        <v>766</v>
+      </c>
+      <c r="F2" s="186" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="186" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="190">
+        <v>1</v>
+      </c>
+      <c r="B3" s="204" t="s">
+        <v>792</v>
+      </c>
+      <c r="C3" s="205"/>
+      <c r="D3" s="206"/>
+      <c r="E3" s="192" t="s">
+        <v>791</v>
+      </c>
+      <c r="F3" s="190" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="190">
+        <f>C19</f>
+        <v>90.800000000000026</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="191">
+        <v>2</v>
+      </c>
+      <c r="B4" s="204" t="s">
+        <v>788</v>
+      </c>
+      <c r="C4" s="205"/>
+      <c r="D4" s="206"/>
+      <c r="E4" s="192" t="s">
+        <v>793</v>
+      </c>
+      <c r="F4" s="191" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="191">
+        <f>G3</f>
+        <v>90.800000000000026</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="191">
+        <v>3</v>
+      </c>
+      <c r="B5" s="204" t="s">
+        <v>788</v>
+      </c>
+      <c r="C5" s="205"/>
+      <c r="D5" s="206"/>
+      <c r="E5" s="192" t="s">
+        <v>794</v>
+      </c>
+      <c r="F5" s="191" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="191">
+        <f>G3</f>
+        <v>90.800000000000026</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="191">
+        <v>4</v>
+      </c>
+      <c r="B6" s="204" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="205"/>
+      <c r="D6" s="206"/>
+      <c r="E6" s="192" t="s">
+        <v>789</v>
+      </c>
+      <c r="F6" s="191" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="191">
+        <f>G3+14.2*0.4*6+12.9*0.4*3</f>
+        <v>140.36000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="191">
+        <v>5</v>
+      </c>
+      <c r="B7" s="204" t="s">
+        <v>772</v>
+      </c>
+      <c r="C7" s="205"/>
+      <c r="D7" s="206"/>
+      <c r="E7" s="192" t="s">
+        <v>790</v>
+      </c>
+      <c r="F7" s="191" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="191">
+        <f xml:space="preserve"> 4 * 3 * 2 * 2.5 + 2*3*3*2*2.5</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="201"/>
+      <c r="B8" s="201"/>
+      <c r="C8" s="201"/>
+      <c r="D8" s="201"/>
+      <c r="E8" s="201"/>
+      <c r="F8" s="201"/>
+      <c r="G8" s="201"/>
+    </row>
+    <row r="9" spans="1:7" s="194" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="190" t="s">
+        <v>784</v>
+      </c>
+      <c r="B9" s="190" t="s">
+        <v>785</v>
+      </c>
+      <c r="C9" s="190" t="s">
+        <v>786</v>
+      </c>
+      <c r="D9" s="207"/>
+      <c r="E9" s="208"/>
+      <c r="F9" s="208"/>
+      <c r="G9" s="208"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="190">
+        <v>1</v>
+      </c>
+      <c r="B10" s="190" t="s">
+        <v>781</v>
+      </c>
+      <c r="C10" s="195">
+        <v>11.22</v>
+      </c>
+      <c r="D10" s="207"/>
+      <c r="E10" s="208"/>
+      <c r="F10" s="208"/>
+      <c r="G10" s="208"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="190">
+        <v>2</v>
+      </c>
+      <c r="B11" s="190" t="s">
+        <v>782</v>
+      </c>
+      <c r="C11" s="195">
+        <v>11.23</v>
+      </c>
+      <c r="D11" s="207"/>
+      <c r="E11" s="208"/>
+      <c r="F11" s="208"/>
+      <c r="G11" s="208"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="190">
+        <v>3</v>
+      </c>
+      <c r="B12" s="190" t="s">
+        <v>783</v>
+      </c>
+      <c r="C12" s="195">
+        <v>11.25</v>
+      </c>
+      <c r="D12" s="207"/>
+      <c r="E12" s="208"/>
+      <c r="F12" s="208"/>
+      <c r="G12" s="208"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="190">
+        <v>4</v>
+      </c>
+      <c r="B13" s="190" t="s">
+        <v>691</v>
+      </c>
+      <c r="C13" s="195">
+        <v>10.130000000000001</v>
+      </c>
+      <c r="D13" s="207"/>
+      <c r="E13" s="208"/>
+      <c r="F13" s="208"/>
+      <c r="G13" s="208"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="190">
+        <v>5</v>
+      </c>
+      <c r="B14" s="190" t="s">
+        <v>730</v>
+      </c>
+      <c r="C14" s="195">
+        <v>10.130000000000001</v>
+      </c>
+      <c r="D14" s="207"/>
+      <c r="E14" s="208"/>
+      <c r="F14" s="208"/>
+      <c r="G14" s="208"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="190">
+        <v>6</v>
+      </c>
+      <c r="B15" s="190" t="s">
+        <v>743</v>
+      </c>
+      <c r="C15" s="195">
+        <v>10.14</v>
+      </c>
+      <c r="D15" s="207"/>
+      <c r="E15" s="208"/>
+      <c r="F15" s="208"/>
+      <c r="G15" s="208"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="190">
+        <v>7</v>
+      </c>
+      <c r="B16" s="190" t="s">
+        <v>602</v>
+      </c>
+      <c r="C16" s="195">
+        <v>8.9</v>
+      </c>
+      <c r="D16" s="207"/>
+      <c r="E16" s="208"/>
+      <c r="F16" s="208"/>
+      <c r="G16" s="208"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="190">
+        <v>8</v>
+      </c>
+      <c r="B17" s="190" t="s">
+        <v>640</v>
+      </c>
+      <c r="C17" s="195">
+        <v>8.9</v>
+      </c>
+      <c r="D17" s="207"/>
+      <c r="E17" s="208"/>
+      <c r="F17" s="208"/>
+      <c r="G17" s="208"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="190">
+        <v>9</v>
+      </c>
+      <c r="B18" s="190" t="s">
+        <v>658</v>
+      </c>
+      <c r="C18" s="195">
+        <v>8.9</v>
+      </c>
+      <c r="D18" s="207"/>
+      <c r="E18" s="208"/>
+      <c r="F18" s="208"/>
+      <c r="G18" s="208"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="202" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="203"/>
+      <c r="C19" s="185">
+        <f>SUM(C10:C18)</f>
+        <v>90.800000000000026</v>
+      </c>
+      <c r="D19" s="207"/>
+      <c r="E19" s="208"/>
+      <c r="F19" s="208"/>
+      <c r="G19" s="208"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="D9:G19"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="9" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="22.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="51" style="4" customWidth="1"/>
+    <col min="2" max="2" width="41.109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="22.33203125" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="212" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="213"/>
+      <c r="C1" s="213"/>
+      <c r="D1" s="213"/>
+      <c r="E1" s="214"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="15">
+        <v>1</v>
+      </c>
+      <c r="E3" s="15">
+        <f>Лист1!B31</f>
+        <v>2126.1999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="14"/>
+      <c r="C4" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="18">
+        <v>0.15</v>
+      </c>
+      <c r="E4" s="18">
+        <f>E3*D4</f>
+        <v>318.92999999999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="14"/>
+      <c r="C5" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="18">
+        <v>4.5</v>
+      </c>
+      <c r="E5" s="18">
+        <f>E3*D5</f>
+        <v>9567.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="15">
+        <v>1</v>
+      </c>
+      <c r="E6" s="15">
+        <f>E3</f>
+        <v>2126.1999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="14"/>
+      <c r="C7" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="18">
+        <v>1.8</v>
+      </c>
+      <c r="E7" s="18">
+        <f>E6*D7</f>
+        <v>3827.16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="14"/>
+      <c r="C8" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="18">
+        <v>0.15</v>
+      </c>
+      <c r="E8" s="18">
+        <f>E6*D8</f>
+        <v>318.92999999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -14606,80 +16463,274 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" style="193" customWidth="1"/>
-    <col min="2" max="2" width="28.109375" style="193" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" style="193" customWidth="1"/>
-    <col min="4" max="4" width="9.44140625" style="193" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="193"/>
+    <col min="1" max="1" width="7.77734375" style="184" customWidth="1"/>
+    <col min="2" max="2" width="38" style="184" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="184" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" style="184" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="184"/>
+    <col min="6" max="6" width="13.21875" style="184" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="184"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="200" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
+      <c r="B1" s="200"/>
+      <c r="C1" s="200"/>
+      <c r="D1" s="200"/>
+      <c r="E1" s="200"/>
+      <c r="F1" s="200"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="194" t="s">
+      <c r="A2" s="185" t="s">
         <v>764</v>
       </c>
-      <c r="B2" s="194" t="s">
+      <c r="B2" s="185" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="195" t="s">
+      <c r="C2" s="186" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="195" t="s">
+      <c r="D2" s="186" t="s">
         <v>767</v>
       </c>
-      <c r="E2" s="195" t="s">
+      <c r="E2" s="186" t="s">
         <v>765</v>
       </c>
-      <c r="F2" s="195" t="s">
-        <v>17</v>
+      <c r="F2" s="186" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="196">
+      <c r="A3" s="187">
         <v>1</v>
       </c>
-      <c r="B3" s="197" t="s">
+      <c r="B3" s="188" t="s">
         <v>768</v>
       </c>
-      <c r="C3" s="196" t="s">
+      <c r="C3" s="187" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="195">
+      <c r="D3" s="186">
         <f>5.2*0.38+0.69</f>
         <v>2.6660000000000004</v>
       </c>
-      <c r="E3" s="196">
+      <c r="E3" s="187">
         <v>5</v>
       </c>
-      <c r="F3" s="196">
+      <c r="F3" s="187">
         <f>D3*E3</f>
         <v>13.330000000000002</v>
       </c>
     </row>
+    <row r="4" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="187">
+        <v>2</v>
+      </c>
+      <c r="B4" s="188" t="s">
+        <v>769</v>
+      </c>
+      <c r="C4" s="187" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="186">
+        <f>5.2*0.38+0.69</f>
+        <v>2.6660000000000004</v>
+      </c>
+      <c r="E4" s="187">
+        <v>5</v>
+      </c>
+      <c r="F4" s="187">
+        <f>D4*E4</f>
+        <v>13.330000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="187">
+        <v>3</v>
+      </c>
+      <c r="B5" s="188" t="s">
+        <v>770</v>
+      </c>
+      <c r="C5" s="187" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="186">
+        <f>5.2*0.38+0.69</f>
+        <v>2.6660000000000004</v>
+      </c>
+      <c r="E5" s="187">
+        <v>5</v>
+      </c>
+      <c r="F5" s="187">
+        <f>D5*E5</f>
+        <v>13.330000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="187">
+        <v>4</v>
+      </c>
+      <c r="B6" s="188" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="187" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="186">
+        <f>5.2*0.38+0.69</f>
+        <v>2.6660000000000004</v>
+      </c>
+      <c r="E6" s="187">
+        <v>5</v>
+      </c>
+      <c r="F6" s="187">
+        <f>D6*E6</f>
+        <v>13.330000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="189">
+        <v>5</v>
+      </c>
+      <c r="B7" s="188" t="s">
+        <v>772</v>
+      </c>
+      <c r="C7" s="189" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="186" t="s">
+        <v>773</v>
+      </c>
+      <c r="E7" s="189">
+        <v>20</v>
+      </c>
+      <c r="F7" s="189">
+        <f>C14</f>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="201"/>
+      <c r="B8" s="201"/>
+      <c r="C8" s="201"/>
+      <c r="D8" s="201"/>
+      <c r="E8" s="201"/>
+      <c r="F8" s="201"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="200" t="s">
+        <v>780</v>
+      </c>
+      <c r="B9" s="200"/>
+      <c r="C9" s="200"/>
+      <c r="D9" s="200"/>
+      <c r="E9" s="215"/>
+      <c r="F9" s="216"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="185" t="s">
+        <v>774</v>
+      </c>
+      <c r="B10" s="185" t="s">
+        <v>775</v>
+      </c>
+      <c r="C10" s="185">
+        <f>10*2*4</f>
+        <v>80</v>
+      </c>
+      <c r="D10" s="189" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="215"/>
+      <c r="F10" s="216"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="185" t="s">
+        <v>774</v>
+      </c>
+      <c r="B11" s="185" t="s">
+        <v>776</v>
+      </c>
+      <c r="C11" s="185">
+        <f>7.5*2*4</f>
+        <v>60</v>
+      </c>
+      <c r="D11" s="189" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="215"/>
+      <c r="F11" s="216"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="185" t="s">
+        <v>777</v>
+      </c>
+      <c r="B12" s="185" t="s">
+        <v>778</v>
+      </c>
+      <c r="C12" s="185">
+        <f>7.5*2*8</f>
+        <v>120</v>
+      </c>
+      <c r="D12" s="189" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="215"/>
+      <c r="F12" s="216"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="185" t="s">
+        <v>622</v>
+      </c>
+      <c r="B13" s="185" t="s">
+        <v>779</v>
+      </c>
+      <c r="C13" s="185">
+        <f>2.5*2*4</f>
+        <v>20</v>
+      </c>
+      <c r="D13" s="189" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="215"/>
+      <c r="F13" s="216"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="202" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="203"/>
+      <c r="C14" s="185">
+        <f>SUM(C10:C13)</f>
+        <v>280</v>
+      </c>
+      <c r="D14" s="189" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="215"/>
+      <c r="F14" s="216"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="5">
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E9:F14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
@@ -17842,7 +19893,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G49"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -18660,7 +20711,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
@@ -18677,13 +20728,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="187" t="s">
+      <c r="A1" s="217" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="188"/>
-      <c r="C1" s="188"/>
-      <c r="D1" s="188"/>
-      <c r="E1" s="189"/>
+      <c r="B1" s="218"/>
+      <c r="C1" s="218"/>
+      <c r="D1" s="218"/>
+      <c r="E1" s="219"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
@@ -18810,7 +20861,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -24063,15 +26114,15 @@
       <c r="B218" s="124" t="s">
         <v>408</v>
       </c>
-      <c r="C218" s="190" t="s">
+      <c r="C218" s="220" t="s">
         <v>409</v>
       </c>
-      <c r="D218" s="191"/>
-      <c r="E218" s="191"/>
-      <c r="F218" s="191"/>
-      <c r="G218" s="191"/>
-      <c r="H218" s="191"/>
-      <c r="I218" s="191"/>
+      <c r="D218" s="221"/>
+      <c r="E218" s="221"/>
+      <c r="F218" s="221"/>
+      <c r="G218" s="221"/>
+      <c r="H218" s="221"/>
+      <c r="I218" s="221"/>
       <c r="J218" s="143"/>
     </row>
     <row r="219" spans="1:10" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
@@ -25381,961 +27432,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10" style="29" customWidth="1"/>
-    <col min="2" max="16384" width="9.109375" style="29"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="12">
-        <v>3004</v>
-      </c>
-      <c r="B2" s="27">
-        <v>241.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="12">
-        <v>3007</v>
-      </c>
-      <c r="B3" s="27">
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="12">
-        <v>3009</v>
-      </c>
-      <c r="B4" s="27">
-        <v>22.8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
-        <v>3012</v>
-      </c>
-      <c r="B5" s="27">
-        <v>233.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
-        <v>3015</v>
-      </c>
-      <c r="B6" s="27">
-        <v>19.100000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
-        <v>3017</v>
-      </c>
-      <c r="B7" s="27">
-        <v>9.4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
-        <v>3019</v>
-      </c>
-      <c r="B8" s="27">
-        <v>315.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
-        <v>3023</v>
-      </c>
-      <c r="B9" s="27">
-        <v>185.9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="12">
-        <v>3033</v>
-      </c>
-      <c r="B10" s="27">
-        <v>8.8999999999999986</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="12">
-        <v>3037</v>
-      </c>
-      <c r="B11" s="27">
-        <v>111.60000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="12">
-        <v>3041</v>
-      </c>
-      <c r="B12" s="27">
-        <v>159.80000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="12">
-        <v>3042</v>
-      </c>
-      <c r="B13" s="27">
-        <v>21.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="12">
-        <v>3043</v>
-      </c>
-      <c r="B14" s="27">
-        <v>21.8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="12">
-        <v>3045</v>
-      </c>
-      <c r="B15" s="27">
-        <v>4.5999999999999996</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="12">
-        <v>3046</v>
-      </c>
-      <c r="B16" s="27">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="12">
-        <v>3051</v>
-      </c>
-      <c r="B17" s="27">
-        <v>193.7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="12">
-        <v>3053</v>
-      </c>
-      <c r="B18" s="27">
-        <v>198.20000000000002</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="12">
-        <v>3055</v>
-      </c>
-      <c r="B19" s="27">
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="12">
-        <v>3057</v>
-      </c>
-      <c r="B20" s="27">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="12">
-        <v>3059</v>
-      </c>
-      <c r="B21" s="27">
-        <v>38.799999999999997</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="12">
-        <v>3060</v>
-      </c>
-      <c r="B22" s="27">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="12">
-        <v>3061</v>
-      </c>
-      <c r="B23" s="27">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="12">
-        <v>3062</v>
-      </c>
-      <c r="B24" s="27">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="12">
-        <v>3063</v>
-      </c>
-      <c r="B25" s="27">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="12">
-        <v>3064</v>
-      </c>
-      <c r="B26" s="27">
-        <v>14.6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="12">
-        <v>3065</v>
-      </c>
-      <c r="B27" s="27">
-        <v>2.3000000000000003</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="12">
-        <v>3066</v>
-      </c>
-      <c r="B28" s="27">
-        <v>97.600000000000009</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="12">
-        <v>3067</v>
-      </c>
-      <c r="B29" s="27">
-        <v>14.299999999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" s="31">
-        <f>SUM(B2:B29)</f>
-        <v>2056.7999999999997</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H47"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" customWidth="1"/>
-    <col min="5" max="5" width="15.5546875" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="52" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="52" t="s">
-        <v>43</v>
-      </c>
-      <c r="E1" s="52" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="60">
-        <v>3004</v>
-      </c>
-      <c r="B2" s="61">
-        <f>'3пом'!B2</f>
-        <v>241.1</v>
-      </c>
-      <c r="C2" s="61">
-        <v>244.1</v>
-      </c>
-      <c r="D2" s="52">
-        <v>244.9</v>
-      </c>
-      <c r="E2" s="62">
-        <f>B2-D2</f>
-        <v>-3.8000000000000114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="60">
-        <v>3007</v>
-      </c>
-      <c r="B3" s="61">
-        <f>'3пом'!B3</f>
-        <v>8.1</v>
-      </c>
-      <c r="C3" s="61">
-        <v>9.1</v>
-      </c>
-      <c r="D3" s="52">
-        <v>9.1</v>
-      </c>
-      <c r="E3" s="62">
-        <f t="shared" ref="E3:E29" si="0">B3-D3</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="60">
-        <v>3009</v>
-      </c>
-      <c r="B4" s="61">
-        <f>'3пом'!B4</f>
-        <v>22.8</v>
-      </c>
-      <c r="C4" s="61">
-        <v>23.5</v>
-      </c>
-      <c r="D4" s="52">
-        <v>23.5</v>
-      </c>
-      <c r="E4" s="62">
-        <f t="shared" si="0"/>
-        <v>-0.69999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="63">
-        <v>3012</v>
-      </c>
-      <c r="B5" s="64">
-        <f>'3пом'!B5</f>
-        <v>233.5</v>
-      </c>
-      <c r="C5" s="64">
-        <v>470.2</v>
-      </c>
-      <c r="D5" s="65">
-        <v>235.7</v>
-      </c>
-      <c r="E5" s="62">
-        <f t="shared" si="0"/>
-        <v>-2.1999999999999886</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="60">
-        <v>3015</v>
-      </c>
-      <c r="B6" s="61">
-        <f>'3пом'!B6</f>
-        <v>19.100000000000001</v>
-      </c>
-      <c r="C6" s="61">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="D6" s="52">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="E6" s="62">
-        <f t="shared" si="0"/>
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="60">
-        <v>3017</v>
-      </c>
-      <c r="B7" s="61">
-        <f>'3пом'!B7</f>
-        <v>9.4</v>
-      </c>
-      <c r="C7" s="61">
-        <v>10.3</v>
-      </c>
-      <c r="D7" s="52">
-        <v>10.3</v>
-      </c>
-      <c r="E7" s="62">
-        <f t="shared" si="0"/>
-        <v>-0.90000000000000036</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="60">
-        <v>3019</v>
-      </c>
-      <c r="B8" s="61">
-        <f>'3пом'!B8</f>
-        <v>315.5</v>
-      </c>
-      <c r="C8" s="61">
-        <v>321.8</v>
-      </c>
-      <c r="D8" s="52">
-        <v>320.39999999999998</v>
-      </c>
-      <c r="E8" s="62">
-        <f t="shared" si="0"/>
-        <v>-4.8999999999999773</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="63">
-        <v>3023</v>
-      </c>
-      <c r="B9" s="64">
-        <f>'3пом'!B9</f>
-        <v>185.9</v>
-      </c>
-      <c r="C9" s="64">
-        <v>364.3</v>
-      </c>
-      <c r="D9" s="65">
-        <v>188.6</v>
-      </c>
-      <c r="E9" s="62">
-        <f t="shared" si="0"/>
-        <v>-2.6999999999999886</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="60">
-        <v>3033</v>
-      </c>
-      <c r="B10" s="61">
-        <f>'3пом'!B10</f>
-        <v>8.8999999999999986</v>
-      </c>
-      <c r="C10" s="61">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="D10" s="52">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="E10" s="62">
-        <f t="shared" si="0"/>
-        <v>-0.30000000000000071</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="63">
-        <v>3037</v>
-      </c>
-      <c r="B11" s="64">
-        <f>'3пом'!B11</f>
-        <v>111.60000000000001</v>
-      </c>
-      <c r="C11" s="64">
-        <v>232.5</v>
-      </c>
-      <c r="D11" s="65">
-        <v>116.4</v>
-      </c>
-      <c r="E11" s="62">
-        <f t="shared" si="0"/>
-        <v>-4.7999999999999972</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="63">
-        <v>3041</v>
-      </c>
-      <c r="B12" s="64">
-        <f>'3пом'!B12</f>
-        <v>159.80000000000001</v>
-      </c>
-      <c r="C12" s="64">
-        <v>331.2</v>
-      </c>
-      <c r="D12" s="65">
-        <v>165.8</v>
-      </c>
-      <c r="E12" s="62">
-        <f t="shared" si="0"/>
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="60">
-        <v>3042</v>
-      </c>
-      <c r="B13" s="61">
-        <f>'3пом'!B13</f>
-        <v>21.4</v>
-      </c>
-      <c r="C13" s="61">
-        <v>22.2</v>
-      </c>
-      <c r="D13" s="52">
-        <v>22.2</v>
-      </c>
-      <c r="E13" s="62">
-        <f t="shared" si="0"/>
-        <v>-0.80000000000000071</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="60">
-        <v>3043</v>
-      </c>
-      <c r="B14" s="61">
-        <f>'3пом'!B14</f>
-        <v>21.8</v>
-      </c>
-      <c r="C14" s="61">
-        <v>22.1</v>
-      </c>
-      <c r="D14" s="52">
-        <v>22.1</v>
-      </c>
-      <c r="E14" s="62">
-        <f t="shared" si="0"/>
-        <v>-0.30000000000000071</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="60">
-        <v>3045</v>
-      </c>
-      <c r="B15" s="61">
-        <f>'3пом'!B15</f>
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="C15" s="61">
-        <v>5.6</v>
-      </c>
-      <c r="D15" s="52">
-        <v>5.6</v>
-      </c>
-      <c r="E15" s="62">
-        <f t="shared" si="0"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="60">
-        <v>3046</v>
-      </c>
-      <c r="B16" s="61">
-        <f>'3пом'!B16</f>
-        <v>9</v>
-      </c>
-      <c r="C16" s="61">
-        <v>9.1</v>
-      </c>
-      <c r="D16" s="52">
-        <v>9.1</v>
-      </c>
-      <c r="E16" s="62">
-        <f t="shared" si="0"/>
-        <v>-9.9999999999999645E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="63">
-        <v>3051</v>
-      </c>
-      <c r="B17" s="64">
-        <f>'3пом'!B17</f>
-        <v>193.7</v>
-      </c>
-      <c r="C17" s="64">
-        <v>363.8</v>
-      </c>
-      <c r="D17" s="65">
-        <v>198.1</v>
-      </c>
-      <c r="E17" s="62">
-        <f t="shared" si="0"/>
-        <v>-4.4000000000000057</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="60">
-        <v>3053</v>
-      </c>
-      <c r="B18" s="61">
-        <f>'3пом'!B18</f>
-        <v>198.20000000000002</v>
-      </c>
-      <c r="C18" s="61">
-        <v>200.9</v>
-      </c>
-      <c r="D18" s="52">
-        <v>200.9</v>
-      </c>
-      <c r="E18" s="62">
-        <f t="shared" si="0"/>
-        <v>-2.6999999999999886</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="60">
-        <v>3055</v>
-      </c>
-      <c r="B19" s="61">
-        <f>'3пом'!B19</f>
-        <v>13.8</v>
-      </c>
-      <c r="C19" s="61">
-        <v>14.5</v>
-      </c>
-      <c r="D19" s="52">
-        <v>14.5</v>
-      </c>
-      <c r="E19" s="62">
-        <f t="shared" si="0"/>
-        <v>-0.69999999999999929</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="60">
-        <v>3057</v>
-      </c>
-      <c r="B20" s="61">
-        <f>'3пом'!B20</f>
-        <v>8</v>
-      </c>
-      <c r="C20" s="61">
-        <v>8.6</v>
-      </c>
-      <c r="D20" s="52">
-        <v>8.6</v>
-      </c>
-      <c r="E20" s="62">
-        <f t="shared" si="0"/>
-        <v>-0.59999999999999964</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="60">
-        <v>3059</v>
-      </c>
-      <c r="B21" s="61">
-        <f>'3пом'!B21</f>
-        <v>38.799999999999997</v>
-      </c>
-      <c r="C21" s="61">
-        <v>39</v>
-      </c>
-      <c r="D21" s="52">
-        <v>39</v>
-      </c>
-      <c r="E21" s="62">
-        <f t="shared" si="0"/>
-        <v>-0.20000000000000284</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="60">
-        <v>3060</v>
-      </c>
-      <c r="B22" s="61">
-        <f>'3пом'!B22</f>
-        <v>7.5</v>
-      </c>
-      <c r="C22" s="61">
-        <v>7.6</v>
-      </c>
-      <c r="D22" s="52">
-        <v>7.6</v>
-      </c>
-      <c r="E22" s="62">
-        <f t="shared" si="0"/>
-        <v>-9.9999999999999645E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="60">
-        <v>3061</v>
-      </c>
-      <c r="B23" s="61">
-        <f>'3пом'!B23</f>
-        <v>12</v>
-      </c>
-      <c r="C23" s="61">
-        <v>12.8</v>
-      </c>
-      <c r="D23" s="52">
-        <v>12.8</v>
-      </c>
-      <c r="E23" s="62">
-        <f t="shared" si="0"/>
-        <v>-0.80000000000000071</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="60">
-        <v>3062</v>
-      </c>
-      <c r="B24" s="61">
-        <f>'3пом'!B24</f>
-        <v>11.5</v>
-      </c>
-      <c r="C24" s="61">
-        <v>11.8</v>
-      </c>
-      <c r="D24" s="62">
-        <f>B24</f>
-        <v>11.5</v>
-      </c>
-      <c r="E24" s="62">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="60">
-        <v>3063</v>
-      </c>
-      <c r="B25" s="61">
-        <f>'3пом'!B25</f>
-        <v>72</v>
-      </c>
-      <c r="C25" s="61">
-        <v>72.8</v>
-      </c>
-      <c r="D25" s="62">
-        <f t="shared" ref="D25:D27" si="1">B25</f>
-        <v>72</v>
-      </c>
-      <c r="E25" s="62">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="60">
-        <v>3064</v>
-      </c>
-      <c r="B26" s="61">
-        <f>'3пом'!B26</f>
-        <v>14.6</v>
-      </c>
-      <c r="C26" s="61">
-        <v>15.6</v>
-      </c>
-      <c r="D26" s="62">
-        <f t="shared" si="1"/>
-        <v>14.6</v>
-      </c>
-      <c r="E26" s="62">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="60">
-        <v>3065</v>
-      </c>
-      <c r="B27" s="61">
-        <f>'3пом'!B27</f>
-        <v>2.3000000000000003</v>
-      </c>
-      <c r="C27" s="61">
-        <v>3.2</v>
-      </c>
-      <c r="D27" s="62">
-        <f t="shared" si="1"/>
-        <v>2.3000000000000003</v>
-      </c>
-      <c r="E27" s="62">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="60">
-        <v>3066</v>
-      </c>
-      <c r="B28" s="61">
-        <f>'3пом'!B28</f>
-        <v>97.600000000000009</v>
-      </c>
-      <c r="C28" s="61">
-        <v>102.2</v>
-      </c>
-      <c r="D28" s="52">
-        <v>101.7</v>
-      </c>
-      <c r="E28" s="62">
-        <f t="shared" si="0"/>
-        <v>-4.0999999999999943</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="60">
-        <v>3067</v>
-      </c>
-      <c r="B29" s="61">
-        <f>'3пом'!B29</f>
-        <v>14.299999999999999</v>
-      </c>
-      <c r="C29" s="61">
-        <v>15.3</v>
-      </c>
-      <c r="D29" s="52">
-        <v>15.2</v>
-      </c>
-      <c r="E29" s="62">
-        <f t="shared" si="0"/>
-        <v>-0.90000000000000036</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B30" s="20">
-        <f>SUM(B2:B29)</f>
-        <v>2056.7999999999997</v>
-      </c>
-      <c r="C30" s="20">
-        <f>SUM(C2:C29)</f>
-        <v>2962.9</v>
-      </c>
-      <c r="D30" s="20">
-        <f t="shared" ref="D30:E30" si="2">SUM(D2:D29)</f>
-        <v>2101.2999999999993</v>
-      </c>
-      <c r="E30" s="20">
-        <f t="shared" si="2"/>
-        <v>-44.49999999999995</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D31" s="58"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="25">
-        <v>3006</v>
-      </c>
-      <c r="B33" s="26"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="21">
-        <v>3016</v>
-      </c>
-      <c r="B34" s="22"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="25">
-        <v>3020</v>
-      </c>
-      <c r="B35" s="26"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="25">
-        <v>3024</v>
-      </c>
-      <c r="B36" s="26"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="25">
-        <v>3034</v>
-      </c>
-      <c r="B37" s="26"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="23">
-        <v>3047</v>
-      </c>
-      <c r="B38" s="24"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="21">
-        <v>3052</v>
-      </c>
-      <c r="B39" s="22"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G40" t="s">
-        <v>28</v>
-      </c>
-      <c r="H40" s="20">
-        <f>B17+B18+B21+B22+B23+B24</f>
-        <v>461.7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G41" t="s">
-        <v>29</v>
-      </c>
-      <c r="H41" s="20">
-        <f>SUM(B11:B16)+B27</f>
-        <v>330.50000000000006</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G42" t="s">
-        <v>30</v>
-      </c>
-      <c r="H42" s="44">
-        <f>B10+B28+B19+B20+B26</f>
-        <v>142.9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G43" t="s">
-        <v>31</v>
-      </c>
-      <c r="H43" s="20">
-        <f>B8+B9+B25</f>
-        <v>573.4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G44" t="s">
-        <v>32</v>
-      </c>
-      <c r="H44" s="20">
-        <f>SUM(B5:B7)+B29</f>
-        <v>276.3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G45" t="s">
-        <v>33</v>
-      </c>
-      <c r="H45" s="20">
-        <f>SUM(B2:B4)</f>
-        <v>272</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H46" s="20">
-        <f>B30</f>
-        <v>2056.7999999999997</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H47" s="20">
-        <f>SUM(H40:H45)-H46</f>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>